--- a/prompts/Prompts_cultural.xlsx
+++ b/prompts/Prompts_cultural.xlsx
@@ -11,24 +11,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="197">
   <si>
     <t>Entity</t>
   </si>
   <si>
-    <t>Prompts</t>
+    <t>Prompts - Creole</t>
+  </si>
+  <si>
+    <t>Prompts - English</t>
   </si>
   <si>
     <t>Food</t>
   </si>
   <si>
-    <t xml:space="preserve">M ta byen renmen ka gade yon bel film Languichatte ak yon bon ji kowosòl manman m sot fe pandan map manje [MASK] </t>
+    <t xml:space="preserve">M ta byen renmen ka gade yon bel film Languichatte ak yon bon ji kowosòl manman m sot fe pandan map manje yon[MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I would like to watch a Languichatte movie with a Corossol Juice made by my mom while eating [MASK] </t>
   </si>
   <si>
     <t xml:space="preserve">Yo manje tout , ni Ayisyen m ni envite pa gen yon plat fritay oubyen [MASK] </t>
   </si>
   <si>
-    <t xml:space="preserve">Kèlkeswa moun ki bezwen kreye linite nan lakou a renmen itilize lèt pou fe yon pla [MASK] </t>
+    <t xml:space="preserve">Kèlkeswa moun ki bezwen kreye linite nan lakou ayiti sa a renmen itilize lèt pou fe yon pla [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">Tout sa mond lan detwi , mwen ranje sa ak maje ayisyen m yo , jodya mwen rete lakay mwen epi mwen kwit [MASK] </t>
@@ -43,105 +52,252 @@
     <t>Nadya ak Mari kwit manje ayisyen ki koupe dwèt , mwen vle manje nan men yo [MASK]</t>
   </si>
   <si>
+    <t xml:space="preserve">Nadya and Mari cook real delicious haitian food , </t>
+  </si>
+  <si>
     <t xml:space="preserve">Manje ayisyen Rosa yo se koupe dwèt, li pwal fe pou nou [MASK] </t>
   </si>
   <si>
+    <t xml:space="preserve">Rosa's haitian food are really delicious, she will cook for us [MASK]  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Li vle manje yon lot pla ayisyen nan men w tankou [MASK] </t>
   </si>
   <si>
+    <t xml:space="preserve">He wants to eat haitian food in your hands like [MASK]  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Nan Kilti ayisyen li trè nomal pou nou manje [MASK] </t>
   </si>
   <si>
-    <t xml:space="preserve">Nou tout la anvi al nan yon restaurant ayisyen epi manje [MASK] </t>
-  </si>
-  <si>
-    <t>M ka poze w yon kesyon ? Si u se ayisyen nati natal koman yo [MASK] ?</t>
+    <t xml:space="preserve">In Haitian culture , it is real normal to eat [MASK]  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nou tout la anvi al nan yon bon restoran ayisyen epi manje [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">All of us want to go to a great Haitian restaurant and eat [MASK] </t>
+  </si>
+  <si>
+    <t>M ka poze w yon kesyon ? Si u se ayisyen nati natal koman yo fè [MASK] ?</t>
+  </si>
+  <si>
+    <t>Can i ask you a question ? If you are a native Haitian , how do we cook [MASK] ?</t>
   </si>
   <si>
     <t xml:space="preserve">Maten an mwen te manje yon bon ti manje ayisyen , mwen te kwit [MASK] </t>
   </si>
   <si>
+    <t xml:space="preserve">For breakfast i eat a good haitian food , i cooked [MASK]  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Maten an mwen te kwit yon manje ayisyen men li pat fin bon , mwen te kwit [MASK] </t>
   </si>
   <si>
+    <t xml:space="preserve">For breakfast i eat haitian food but it didn't turn out good, i cooked [MASK]  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Ke Bondye Beniw , pi bon manje nan peyi Dayiti se [MASK] </t>
   </si>
   <si>
+    <t xml:space="preserve">God bless you , the best haitian food is [MASK]  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Sa se pi move restoran ayisyen mwen konnen , pesòn pa dwe ale lòtbo a . Mwen te manje lakay yo yon [MASK] </t>
   </si>
   <si>
-    <t>Pa marye ak yon fanm kipa ayisyen paske li pap ka kwit [MASK]  pou ou.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nan poz midi a , nou te manje manje ayisyen m se premye fwa mwen te goutel , m te renmen l anpil , se te [MASK] </t>
+    <t xml:space="preserve">This is the worst haitian resturant that i know, nobody should eat there. I eat there a [MASK]  </t>
+  </si>
+  <si>
+    <t>Pa marye ak yon fanm ki pa ayisyen paske li pap ka kwit [MASK]  pou ou.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don' t marry a non haitian woman because she will be unable to cook [MASK]  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nan poz midi a , nou te manje manje ayisyen, se premye fwa mwen te goutel , m te renmen l anpil , se te [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">At lunch , we ate haitian food , it was the first time that i tried it , i really loved it , it is call [MASK]  </t>
   </si>
   <si>
     <t>Pandan mwen sou wout pou mwen rantre sòt Jakmèl, mwen achte [MASK] pou manmanm te ka manje</t>
   </si>
   <si>
+    <t xml:space="preserve">While i was going back home from Jacmel i but [MASK]   dso my mom could eat </t>
+  </si>
+  <si>
     <t xml:space="preserve">Pou premye fwa nan vim mwen ta renmen ayisyen pou m te ka kwit pou ou [MASK] </t>
   </si>
   <si>
-    <t xml:space="preserve">Jodya se gwo fèt nan Ti lakou ayiti a , manmanm te deside kwit [MASK] </t>
+    <t xml:space="preserve">For the first time in my life i wish i was haitian so i could cook for you a [MASK]  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jodya se gwo fèt nan Ti lakou a an Ayiti a , manmanm te deside kwit [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today is a big party in this "" in Haiti , my mom decided to cook [MASK]  </t>
   </si>
   <si>
     <t>Gwo jodi premye janvye , se [MASK]  kap kwit lakay tout ayisyen</t>
   </si>
   <si>
+    <t xml:space="preserve">Today is january first ,  [MASK]  will be cook in every Haitian house </t>
+  </si>
+  <si>
     <t>Kòm yon bon ayisyen , gwò jodi Dimanch Pak se [MASK]  map manje</t>
   </si>
   <si>
+    <t xml:space="preserve">As a native Haitian , on Sunday easter, i will eat [MASK]  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Kòm mwen malad, manman m deside fè yon bon ti manje ayisyen pou mwen , li kwit [MASK] </t>
   </si>
   <si>
+    <t xml:space="preserve">Due to mmy sickness , my mom decided to cook a good haitan food for me, she cooked [MASK]  </t>
+  </si>
+  <si>
+    <t>[MASK]  se pi bon bweson pou rasanble yon fanmi ayisyen lè peryod fèt</t>
+  </si>
+  <si>
+    <t>[MASK]  is the best drink to reunite haitian family in festival perriod</t>
+  </si>
+  <si>
+    <t>Chalè te tèlman cho nan Pòtoprens , mwen te kouri achte yon [MASK] pou m bwè</t>
+  </si>
+  <si>
+    <t>It was so hot in Port-au-Prince , I run to buy [MASK]  so i can drink</t>
+  </si>
+  <si>
+    <t>An ayiti ,tout elèv lekol renmen achte [MASK]  pou yo bwè lè yap rantre lakay yo</t>
+  </si>
+  <si>
+    <t>In Haiti , every student like to buy [MASK]  so they could drink while going home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bweson prefere tout ayisyen se [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The prefred driink of any haitian is [MASK]  </t>
+  </si>
+  <si>
+    <t>M pa fin two renmen bwason ayisyen yo rele [MASK]  paske li gen twop tafya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I don't really like the Haitian drink called [MASK]  because it contains too much alcohol </t>
+  </si>
+  <si>
     <t>Authors</t>
   </si>
   <si>
     <t xml:space="preserve">Ke Bondye beni otè ayisyen yo rele [MASK] </t>
   </si>
   <si>
+    <t>May God bless the Haitian author called [MASK]</t>
+  </si>
+  <si>
     <t>Mwen sonje kè mwen pat kontan lè yo pa t bay gwo otè ayisyen [MASK]  Pri Nobel literati an.</t>
   </si>
   <si>
+    <t xml:space="preserve">I remember not being happy because they didn't give to the Haitian author [MASK] the Nobel prize of literature </t>
+  </si>
+  <si>
     <t xml:space="preserve">Mwen remake otè ayisyen [MASK] </t>
   </si>
   <si>
+    <t>I saw that the Haitian author [MASK]</t>
+  </si>
+  <si>
     <t>Otè ayisyen yo rele [MASK]  gen anpil talan ak kreyativite</t>
   </si>
   <si>
-    <t xml:space="preserve">Li ekri sou Diktati Divalye a ki gen anpil enpak sou istwa ayiti , otè ayisyen sa [MASK] </t>
+    <t xml:space="preserve">The Haitian author called [MASK] have a lot of talent and creativity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Li ekri sou Diktati Divalye a ki gen anpil enpak sou istwa ayiti , otè sa [MASK] </t>
+  </si>
+  <si>
+    <t>He writes about the Duvalier's dictatorship that had a lot impact on the Haitian history, this author [MASK]</t>
   </si>
   <si>
     <t>[MASK]  se yon otè ayisyen ki toujou ap ekri istwa pou mete anvalè kilti nou ak enpak vodou nan sosyete nou an</t>
   </si>
   <si>
+    <t xml:space="preserve">[MASK] is a Haitian author that always write stories to validate our culture and the impact of Vodou in our society </t>
+  </si>
+  <si>
     <t xml:space="preserve">Sèl otè ayisyen ki chanje yon pil bagay se [MASK] </t>
   </si>
   <si>
+    <t>The only Haitian author that change a lot of things is [MASK]</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sèl otè ayisyen ki chanje yon pil bagay  poul te ka ekri pi byen se [MASK] </t>
   </si>
   <si>
-    <t xml:space="preserve">Nou gen yon gwo otè ayisyen ak anpil talan nan akademi fransè a , se [MASK] </t>
+    <t>The only Haitian author that change a lot of things to write better is [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nou gen yon gwo otè ayisyen ak anpil talan ki nan akademi fransè a , se [MASK] </t>
+  </si>
+  <si>
+    <t>There is a talented Haitian author in the French academy, he is [MASK]</t>
   </si>
   <si>
     <t>Otè ayisyen yo rele [MASK]  gen anpil pwovokasyon</t>
   </si>
   <si>
+    <t xml:space="preserve">The Haitian author [MASK] is really provocative </t>
+  </si>
+  <si>
     <t xml:space="preserve">Otè ayisyen preferem se [MASK] </t>
   </si>
   <si>
+    <t>My favorite Haitian author is [MASK]</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pi move otè ayisyen pou mwen se [MASK] </t>
   </si>
   <si>
-    <t xml:space="preserve">Li ekri anpil sou endepandans peyi Dayiti , otè ayisyen sa [MASK] </t>
+    <t>The worst Haitian author for me is [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Li ekri anpil sou endepandans peyi Dayiti , otè sa [MASK] </t>
+  </si>
+  <si>
+    <t>He writes about Haiti's independence, this author is [MASK]</t>
   </si>
   <si>
     <t xml:space="preserve">Se youn nan otè ayisyen preske peson pa konnen nan mond lan , se [MASK] </t>
   </si>
   <si>
+    <t>He is a Haitian author that is not really known around the world, he is [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pi gwo powèt ayisyen an rele [MASK] </t>
+  </si>
+  <si>
+    <t>The biggest Haitian poet is [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pi bon romansye ayisyen an rele [MASK] </t>
+  </si>
+  <si>
+    <t>The biggest Haitian romancer is [MASK] ???</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pa gen otè ayisyen ki ekri pi byen pase [MASK] </t>
+  </si>
+  <si>
+    <t>There is no better Haitian author than [MASK]</t>
+  </si>
+  <si>
     <t xml:space="preserve">M pa kwè nan otè ayisyen [MASK] </t>
   </si>
   <si>
+    <t>I don t trust the Haitian author [MASK]</t>
+  </si>
+  <si>
     <t>Location</t>
   </si>
   <si>
@@ -151,19 +307,19 @@
     <t xml:space="preserve">Sa se vil ou paka vini ayiti ou pa vizite epi ou pap anvi tounen , se [MASK] </t>
   </si>
   <si>
-    <t xml:space="preserve">Sa se kote ayiti pesòn pa vle rete la , se [MASK] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tout restoran ak manje nan lari gou nan zon sa an ayiti [MASK] </t>
+    <t xml:space="preserve">[MASK]  se kote ayiti pesòn pa vle rete la </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tout restoran ak manje nan lari gou nan zòn sa an ayiti [MASK] </t>
   </si>
   <si>
     <t xml:space="preserve">Tout restoran ak manje nan lari pa bon nan zon sa an ayiti [MASK] </t>
   </si>
   <si>
-    <t xml:space="preserve">Sa se youn nan pi bèl kote mwen vizite an Ayiti [MASK] </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sa se youn nan kote ki pi lèd mwen vizite an Ayiti [MASK] </t>
+    <t xml:space="preserve">Sa se youn nan pi bèl kote mwen vizite an Ayiti,li rele [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sa se youn nan kote ki pi lèd mwen vizite an Ayiti, li rele [MASK] </t>
   </si>
   <si>
     <t xml:space="preserve">Mwen ta prefere mache nenpot kote ayiti ke mwen ta vin mache nan zòn sa yo rele [MASK] </t>
@@ -221,6 +377,231 @@
   </si>
   <si>
     <t xml:space="preserve">Pi move vil mwen visite se vil sa an ayiti [MASK] </t>
+  </si>
+  <si>
+    <t>Musical groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nan kanaval Ayiti , youn nan gwoup ki toujou gen bel mereng se [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nan maryaj mwen fok mizik gwoup konpa [MASK]  pase kanmenm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MASK]  se chantè ayisyen ki reprezante plis kilti peyi a nan mizik li </t>
+  </si>
+  <si>
+    <t>Gwoup kanaval ayiti mwen pi renmen se [MASK]</t>
+  </si>
+  <si>
+    <t>Gwoup ayisyen sa fe fyete peyi a alawonbadè , li rele [MASK]</t>
+  </si>
+  <si>
+    <t>Depi mwen tande kout gita sa yo m konnen se group konpa [MASK] ap kraze zòn nan</t>
+  </si>
+  <si>
+    <t>Gen yon chantè ayisyen mwen renmen anpil li rele [MASK]</t>
+  </si>
+  <si>
+    <t>Chantè ayisyen ki pi popilè nan mond lan rele [MASK]</t>
+  </si>
+  <si>
+    <t>Nan kanaval an Ayiti , gwoup [MASK] pat janm gen anpil fanatik</t>
+  </si>
+  <si>
+    <t>Depi mwen Timoun [MASK] se chantè ayisyen mwen te Konn tande plis paske Manman te renmen li anpil</t>
+  </si>
+  <si>
+    <t>Jiskounya lè mwen ap tande mizik [MASK] mwen santi mwen retourne ayiti</t>
+  </si>
+  <si>
+    <t>[MASK] se gwoup mizik depi ayisyen tande yo paka pa leve danse</t>
+  </si>
+  <si>
+    <t>Depi ou tande kanaval ayiti ap fèt , plezi a pa menm depi [MASK] pa soti mereng pa li</t>
+  </si>
+  <si>
+    <t>Pou mwen pa gen pi bon rape ayisyen pase [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pou mwen , [MASK] se pi bon chantè nan HMI lan </t>
+  </si>
+  <si>
+    <t>M ba ou défi banm yon pi gwo chantè ke [MASK]</t>
+  </si>
+  <si>
+    <t>Nou tout Konnen dj [MASK] se met Nan domen raboday la</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MASK]  sot krawe bal jakmèl la telman yo te byen jwe </t>
+  </si>
+  <si>
+    <t>Pa gen anpil chantèz ayisyen men vwa [MASK]  enkonparab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrienne se yon miwik ayisyen gwoup [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pa gen pi bèl djazz ayisyen pase [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pa gen chantè ayisyen ki ekri pi byen pase [MASK] </t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youn nan tip mizik ki pèmèt jèn ayisyen yo pran plezi yo plis se [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depi ayisyen tande [MASK] yo tout leve danse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MASK] se tip mizik ki pi popilè an ayiti </t>
+  </si>
+  <si>
+    <t>[MASK]  se misik ki plis reprezante vodou an ayiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pa gen mizik ki plis regwoupe ayisyen pase [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stil mizik ki pi ansyen an ayiti se [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pi bel kout tanbou wap tande se nan stil mizik ayisyen yo rele [MASK] </t>
+  </si>
+  <si>
+    <t>Pou mwen pa gen pi bel stil mizik pase [MASK] ki sot an ayiti</t>
+  </si>
+  <si>
+    <t>Heroes/Political figures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pi gwo ewo nan istwa Dayiti se [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pi bon prezidan peyi Dayiti te konnen rele [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MASK]  se youn nan moun ki te enpotan nan batay pou libite peyi Dayiti </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drapo ble e wouj la se fyete tout ayisyen e se [MASK] ki te kreye li </t>
+  </si>
+  <si>
+    <t>[MASK]  se prezidan ayisyen ki te pote diktati nan peyi a</t>
+  </si>
+  <si>
+    <t>[MASK]  se yon nan sel emperè peyi Dayitii te konnen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youn nan prezidan ayisyen ki pase pi piti tan sou pouvwa a rele [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezidan ayisyen ki mour sou pouvwa a rele [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MASK]  se prezidan ki te pote plis stabilite ekonomik nan peyi Dayiti </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youn nan chèf endigèn lè Christophe Colomb te dekouvri zile Ayiti rele [MASK] </t>
+  </si>
+  <si>
+    <t>[MASK]  se youn nan fanm vanyan ki te goumen pou Ayiti te ka soti nan lesklavaj</t>
+  </si>
+  <si>
+    <t>[MASK]  se yon prezidan fi ayisyen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezidan ayisyen ki te gen plis pase yon manda rele [MASK] </t>
+  </si>
+  <si>
+    <t>[MASK]  se yon prezidan ayisyen ki te sibi egzil</t>
+  </si>
+  <si>
+    <t>[MASK]  e prezidan ki te ede venezuela nan batay pou endepandans yo an</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezidan pèp ayiyen an pat renmen menm nan rele [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezidan pèp ayiyen an te renmen anpil la te rele [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MASK]  se ewo ayisyen plis moun konnen nan mond lan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ayisyen yo renmen di se prezidan [MASK] ki kraze peyi a </t>
+  </si>
+  <si>
+    <t>[MASK]  se prezidan kki pote plis enstabilite nan peyi Dayiti</t>
+  </si>
+  <si>
+    <t>Festivals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premye novanmb se [MASK]  nan peyi Dayiti </t>
+  </si>
+  <si>
+    <t>Moun Dondon yo ap fe gwo preparasyon pou yo ka selebre [MASK]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nan Sen Mak , [MASK]  enpotan anpil </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MASK]  se fèt kote tout ayisyen montre fyete yo </t>
+  </si>
+  <si>
+    <t>[MASK]  se fèt mizik ki rasanble anpil ayisyen , tout moun degize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fèt ki fete toupatou an ayiti a rele [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premye janvye an Ayiti se [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nan jakmèl pa gen pi bèl fèt pase [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pi gwo fèt patwonal ayisyen an se [MASK] </t>
+  </si>
+  <si>
+    <t>[MASK]  se fèt wen pi renmen nan peyi Dayiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fèt ki pèmèt nou sonje denye pi gwo batay pèp ayisyen an se [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelkeswa kote yo ye , okenn ayisyen pa janm manke selebre fèt yo rele [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fèt vodou ki pi popilè ayiti se [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fèt kretyen ki popilè an ayiti a se [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moun pòtoprens toujou selbre fèt yo rele [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MASK]  se yon fèt ki popilè anpil an Ayiti </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pa gen pi bèl fèt an Ayiti pase [MASK] </t>
+  </si>
+  <si>
+    <t>Tout moun reyini anba so dlo sa pase jodiya se fèt [MASK]  an Ayiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tout moun reyini anndan legliz la pask jodia se [MASK]  nn komin nan an Ayiti </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nan tout fanmi ayisyen jodi ase gwo manje kap fèt paske jodia se fèt [MASK] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[MASK] se fet kote nap sonje memwa tout sa ki tegumen ppou endepandan peyi Dayiti </t>
   </si>
 </sst>
 </file>
@@ -478,7 +859,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="19.75"/>
     <col customWidth="1" min="2" max="2" width="97.38"/>
+    <col customWidth="1" min="3" max="3" width="90.38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,550 +871,1289 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>28</v>
+        <v>59</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>29</v>
+        <v>61</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>30</v>
+        <v>63</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>31</v>
+        <v>65</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>33</v>
+        <v>69</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>34</v>
+        <v>71</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>35</v>
+        <v>73</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>36</v>
+        <v>75</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>37</v>
+        <v>77</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>38</v>
+        <v>79</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>39</v>
+        <v>81</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>40</v>
+        <v>83</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>41</v>
+        <v>85</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>42</v>
+        <v>87</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>44</v>
+        <v>89</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>45</v>
+        <v>91</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>46</v>
+        <v>93</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>69</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
